--- a/public/docs/import_prospects.xlsx
+++ b/public/docs/import_prospects.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\FADWA\ERP\api_0.1\public\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C95341B9-CEC3-4781-890F-F2BE9A2F4B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1F0A2C9-AEDA-444C-AF76-C77AEEE79486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="50" yWindow="1900" windowWidth="19150" windowHeight="7360" xr2:uid="{9D75755E-FE6E-4BAB-BDD4-4CD9ECED924A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{9D75755E-FE6E-4BAB-BDD4-4CD9ECED924A}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>cin</t>
   </si>
@@ -48,31 +48,7 @@
     <t>ville</t>
   </si>
   <si>
-    <t>cin_25</t>
-  </si>
-  <si>
-    <t>n-1</t>
-  </si>
-  <si>
-    <t>p-1</t>
-  </si>
-  <si>
-    <t>n-1@gmail.com</t>
-  </si>
-  <si>
-    <t>meknes</t>
-  </si>
-  <si>
     <t>source</t>
-  </si>
-  <si>
-    <t>Avito</t>
-  </si>
-  <si>
-    <t>+212678985544</t>
-  </si>
-  <si>
-    <t>+212678655997</t>
   </si>
   <si>
     <t>partenaire</t>
@@ -476,43 +452,19 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" t="s">
-        <v>13</v>
-      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="3"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{95488E9E-1B8F-433E-9BC8-301612A07745}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/public/docs/import_prospects.xlsx
+++ b/public/docs/import_prospects.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\FADWA\ERP\api_0.1\public\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1F0A2C9-AEDA-444C-AF76-C77AEEE79486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC9FB8C-1BB0-437A-8126-65FA04A0536B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{9D75755E-FE6E-4BAB-BDD4-4CD9ECED924A}"/>
   </bookViews>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
-  <si>
-    <t>cin</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>nom</t>
   </si>
@@ -49,9 +46,6 @@
   </si>
   <si>
     <t>source</t>
-  </si>
-  <si>
-    <t>partenaire</t>
   </si>
 </sst>
 </file>
@@ -422,14 +416,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E0F0443-92CC-4029-AE8D-C9742B61B601}">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="4" width="34.453125" customWidth="1"/>
-    <col min="5" max="5" width="23.08984375" customWidth="1"/>
+    <col min="3" max="3" width="34.453125" customWidth="1"/>
+    <col min="4" max="4" width="23.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -451,17 +445,11 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="3"/>
+      <c r="E2" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/docs/import_prospects.xlsx
+++ b/public/docs/import_prospects.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\FADWA\ERP\api_0.1\public\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC9FB8C-1BB0-437A-8126-65FA04A0536B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A9C1629-441F-48B2-B7BF-A21B9AFB27DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{9D75755E-FE6E-4BAB-BDD4-4CD9ECED924A}"/>
   </bookViews>

--- a/public/docs/import_prospects.xlsx
+++ b/public/docs/import_prospects.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\FADWA\ERP\api_0.1\public\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A9C1629-441F-48B2-B7BF-A21B9AFB27DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDACF053-A2C4-40F4-B9B0-D7BB8A30D27A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{9D75755E-FE6E-4BAB-BDD4-4CD9ECED924A}"/>
   </bookViews>
@@ -419,7 +419,7 @@
   <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="34.453125" customWidth="1"/>
+    <col min="3" max="3" width="14.54296875" customWidth="1"/>
     <col min="4" max="4" width="23.08984375" customWidth="1"/>
   </cols>
   <sheetData>
